--- a/data/catalog.xlsx
+++ b/data/catalog.xlsx
@@ -56,12 +56,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:E6"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
     <col min="4" max="4" width="8" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -85,6 +86,11 @@
           <t>H</t>
         </is>
       </c>
+      <c r="E1" t="inlineStr" s="1">
+        <is>
+          <t>WEIGHT (kg)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -100,6 +106,9 @@
       </c>
       <c r="D2">
         <v>34.5</v>
+      </c>
+      <c r="E2">
+        <v>27</v>
       </c>
     </row>
     <row r="3">
@@ -117,6 +126,9 @@
       <c r="D3">
         <v>34.5</v>
       </c>
+      <c r="E3">
+        <v>48</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -132,6 +144,9 @@
       </c>
       <c r="D4">
         <v>36</v>
+      </c>
+      <c r="E4">
+        <v>25</v>
       </c>
     </row>
     <row r="5">
@@ -149,6 +164,9 @@
       <c r="D5">
         <v>42</v>
       </c>
+      <c r="E5">
+        <v>24</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -165,6 +183,9 @@
       <c r="D6">
         <v>96</v>
       </c>
+      <c r="E6">
+        <v>86</v>
+      </c>
     </row>
   </sheetData>
 </worksheet>
